--- a/output/pdf_financials_xlsx/PNPN.xlsx
+++ b/output/pdf_financials_xlsx/PNPN.xlsx
@@ -44582,10 +44582,10 @@
         </is>
       </c>
       <c r="U335" s="5" t="n">
-        <v>21.001914</v>
+        <v>-21.001914</v>
       </c>
       <c r="V335" s="5" t="n">
-        <v>39.03873</v>
+        <v>-39.03873</v>
       </c>
     </row>
     <row r="336">

--- a/output/pdf_financials_xlsx/PNPN.xlsx
+++ b/output/pdf_financials_xlsx/PNPN.xlsx
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.11645</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.028295</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00187</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.009926000000000001</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.94082</v>
       </c>
     </row>
     <row r="13">
@@ -2090,16 +2090,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.122804</v>
+        <v>-6.239254</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.8617089999999999</v>
+        <v>-0.890004</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.247963</v>
+        <v>-2.249833</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.336229</v>
+        <v>-3.346155</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.491841</v>
@@ -2141,7 +2141,7 @@
         <v>-21.001914</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-39.027927</v>
+        <v>-38.087107</v>
       </c>
     </row>
     <row r="28">
@@ -2212,16 +2212,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.122804</v>
+        <v>-6.239254</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.8617089999999999</v>
+        <v>-0.890004</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.247963</v>
+        <v>-2.249833</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.336229</v>
+        <v>-3.346155</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.491841</v>
@@ -2263,7 +2263,7 @@
         <v>-21.001914</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-39.027927</v>
+        <v>-38.087107</v>
       </c>
     </row>
     <row r="30">
@@ -2544,49 +2544,49 @@
         <v>1.082298</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>3.541243</v>
+        <v>0.151418</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.122392</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.062902</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.070255</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000456</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.535281</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.059383</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.02996</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.007438</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.179272</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.176687</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.275104</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.216365</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>6.61138</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>21.118155</v>
       </c>
     </row>
     <row r="35">
@@ -2666,49 +2666,49 @@
         <v>1.124058</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>3.54336</v>
+        <v>0.153535</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.000941</v>
+        <v>0.123333</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.062902</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.070255</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000456</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.033668</v>
+        <v>0.568949</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.033668</v>
+        <v>0.09305099999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.02996</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.007438</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.179272</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.176687</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.275104</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.216365</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>6.61138</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>21.118155</v>
       </c>
     </row>
     <row r="37">
@@ -3398,49 +3398,49 @@
         <v>0.01442</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0</v>
+        <v>0.058655</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.169723</v>
+        <v>0.047331</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.815065</v>
+        <v>2.752163</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.09160699999999999</v>
+        <v>0.021352</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.004487</v>
+        <v>0.004031</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.634872</v>
+        <v>0.099591</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.281241</v>
+        <v>0.221858</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.222861</v>
+        <v>0.192901</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.086255</v>
+        <v>0.078817</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.289988</v>
+        <v>0.110716</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.288183</v>
+        <v>0.111496</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.682547</v>
+        <v>0.407443</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.301882</v>
+        <v>1.085517</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>7.243492</v>
+        <v>0.632112</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>21.82456</v>
+        <v>0.7064049999999999</v>
       </c>
     </row>
     <row r="49">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -43152,7 +43152,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -56980,7 +56980,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E455" s="5" t="n">

--- a/output/pdf_financials_xlsx/PNPN.xlsx
+++ b/output/pdf_financials_xlsx/PNPN.xlsx
@@ -7503,13 +7503,13 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004764</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.061217</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.478312</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -7823,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.000694</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -9294,13 +9294,13 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004764</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.061217</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.478312</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -9371,13 +9371,13 @@
         <v>-2.555376</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.7926800000000001</v>
+        <v>-0.797444</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.630452</v>
+        <v>-1.691669</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.367316</v>
+        <v>-1.845628</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-2.636697</v>
@@ -30318,7 +30318,11 @@
           <t>Proceeds on private placement</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -36102,7 +36106,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -37962,7 +37970,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -39882,7 +39894,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
